--- a/data/storage_change/Sacramento_Primary_fall_annual_storage_change_summary.xlsx
+++ b/data/storage_change/Sacramento_Primary_fall_annual_storage_change_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K82"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,31 +497,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1942</v>
+        <v>1950</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>50064.14713447471</v>
+        <v>-343747.9351891037</v>
       </c>
       <c r="F2" t="n">
-        <v>-27525.60861514456</v>
+        <v>-742322.6140883863</v>
       </c>
       <c r="G2" t="n">
-        <v>46514.24974402937</v>
+        <v>275280.7480924714</v>
       </c>
       <c r="H2" t="n">
-        <v>46496.64486197539</v>
+        <v>194599.9301629727</v>
       </c>
       <c r="I2" t="n">
-        <v>-25694.97400158481</v>
+        <v>-326819.7296942222</v>
       </c>
       <c r="J2" t="n">
-        <v>39505.46503771075</v>
+        <v>232496.7987375996</v>
       </c>
       <c r="K2" t="n">
-        <v>50064.14713447471</v>
+        <v>-343747.9351891037</v>
       </c>
     </row>
     <row r="3">
@@ -536,31 +536,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1943</v>
+        <v>1951</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
-        <v>425927.1018686637</v>
+        <v>817846.1801457615</v>
       </c>
       <c r="F3" t="n">
-        <v>-61159.71912889594</v>
+        <v>-68409.41570905148</v>
       </c>
       <c r="G3" t="n">
-        <v>363221.5822294077</v>
+        <v>557122.3743954055</v>
       </c>
       <c r="H3" t="n">
-        <v>339285.9478832821</v>
+        <v>364376.2125720126</v>
       </c>
       <c r="I3" t="n">
-        <v>-42657.22333919114</v>
+        <v>-47357.96784552823</v>
       </c>
       <c r="J3" t="n">
-        <v>212769.5087579179</v>
+        <v>170539.0483850499</v>
       </c>
       <c r="K3" t="n">
-        <v>475991.2490031384</v>
+        <v>474098.2449566578</v>
       </c>
     </row>
     <row r="4">
@@ -575,31 +575,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1944</v>
+        <v>1952</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>-656714.5358780733</v>
+        <v>121633.7709213684</v>
       </c>
       <c r="F4" t="n">
-        <v>-495302.1575855559</v>
+        <v>-204083.6692093414</v>
       </c>
       <c r="G4" t="n">
-        <v>-23784.33521679266</v>
+        <v>267241.9438867778</v>
       </c>
       <c r="H4" t="n">
-        <v>-35168.70600268588</v>
+        <v>153996.8895613432</v>
       </c>
       <c r="I4" t="n">
-        <v>-459534.7461345728</v>
+        <v>-109629.1725939867</v>
       </c>
       <c r="J4" t="n">
-        <v>246042.0759480115</v>
+        <v>90227.50565997059</v>
       </c>
       <c r="K4" t="n">
-        <v>-180723.2868749349</v>
+        <v>595732.0158780261</v>
       </c>
     </row>
     <row r="5">
@@ -614,31 +614,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1948</v>
+        <v>1953</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E5" t="n">
-        <v>-926410.0779648348</v>
+        <v>508889.8014097111</v>
       </c>
       <c r="F5" t="n">
-        <v>-545009.5073502588</v>
+        <v>-66306.69374839317</v>
       </c>
       <c r="G5" t="n">
-        <v>5615.523695203814</v>
+        <v>447129.3085321696</v>
       </c>
       <c r="H5" t="n">
-        <v>3088.538032362092</v>
+        <v>118747.5225681235</v>
       </c>
       <c r="I5" t="n">
-        <v>-349394.8237889624</v>
+        <v>-59122.79980042735</v>
       </c>
       <c r="J5" t="n">
-        <v>164273.7877052459</v>
+        <v>90086.12803899044</v>
       </c>
       <c r="K5" t="n">
-        <v>-1107133.36483977</v>
+        <v>1104621.817287737</v>
       </c>
     </row>
     <row r="6">
@@ -653,31 +653,31 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1949</v>
+        <v>1954</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>-541834.8259686047</v>
+        <v>-951080.817409081</v>
       </c>
       <c r="F6" t="n">
-        <v>-350573.9362357832</v>
+        <v>-397424.995404091</v>
       </c>
       <c r="G6" t="n">
-        <v>60006.49077180912</v>
+        <v>67132.80082930421</v>
       </c>
       <c r="H6" t="n">
-        <v>51435.24990256422</v>
+        <v>26950.27527469485</v>
       </c>
       <c r="I6" t="n">
-        <v>-312660.1187705803</v>
+        <v>-253446.0568574639</v>
       </c>
       <c r="J6" t="n">
-        <v>153937.7491930692</v>
+        <v>116634.0064857332</v>
       </c>
       <c r="K6" t="n">
-        <v>-1648968.190808374</v>
+        <v>153540.9998786562</v>
       </c>
     </row>
     <row r="7">
@@ -692,31 +692,31 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1950</v>
+        <v>1955</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>-338206.8089593274</v>
+        <v>-787603.1929680022</v>
       </c>
       <c r="F7" t="n">
-        <v>-742322.6140883863</v>
+        <v>-243557.0887063384</v>
       </c>
       <c r="G7" t="n">
-        <v>280289.1354125088</v>
+        <v>55520.49606707336</v>
       </c>
       <c r="H7" t="n">
-        <v>196922.928436831</v>
+        <v>19432.17362347566</v>
       </c>
       <c r="I7" t="n">
-        <v>-326819.7296942222</v>
+        <v>-194874.7399738863</v>
       </c>
       <c r="J7" t="n">
-        <v>233073.7793765404</v>
+        <v>77296.70426416534</v>
       </c>
       <c r="K7" t="n">
-        <v>-1987174.999767702</v>
+        <v>-634062.1930893459</v>
       </c>
     </row>
     <row r="8">
@@ -731,31 +731,31 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1951</v>
+        <v>1956</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E8" t="n">
-        <v>817351.5901239421</v>
+        <v>19783.688926791</v>
       </c>
       <c r="F8" t="n">
-        <v>-69723.18832807889</v>
+        <v>-79980.48923367087</v>
       </c>
       <c r="G8" t="n">
-        <v>557122.3743954055</v>
+        <v>179500.063736673</v>
       </c>
       <c r="H8" t="n">
-        <v>364376.2125720126</v>
+        <v>65915.8057596599</v>
       </c>
       <c r="I8" t="n">
-        <v>-47883.47689313919</v>
+        <v>-56983.32526233597</v>
       </c>
       <c r="J8" t="n">
-        <v>170611.0185998417</v>
+        <v>54520.37225269538</v>
       </c>
       <c r="K8" t="n">
-        <v>-1169823.40964376</v>
+        <v>-614278.504162555</v>
       </c>
     </row>
     <row r="9">
@@ -770,31 +770,31 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1952</v>
+        <v>1957</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E9" t="n">
-        <v>122429.3430726142</v>
+        <v>58337.67783987176</v>
       </c>
       <c r="F9" t="n">
-        <v>-204083.6692093414</v>
+        <v>-66360.62687547404</v>
       </c>
       <c r="G9" t="n">
-        <v>267241.9438867778</v>
+        <v>98593.7634357799</v>
       </c>
       <c r="H9" t="n">
-        <v>154036.6681689054</v>
+        <v>67576.50652741085</v>
       </c>
       <c r="I9" t="n">
-        <v>-109629.1725939867</v>
+        <v>-37312.2467271467</v>
       </c>
       <c r="J9" t="n">
-        <v>90261.66200500636</v>
+        <v>32066.7633324335</v>
       </c>
       <c r="K9" t="n">
-        <v>-1047394.066571146</v>
+        <v>-555940.8263226832</v>
       </c>
     </row>
     <row r="10">
@@ -809,31 +809,31 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1953</v>
+        <v>1958</v>
       </c>
       <c r="D10" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E10" t="n">
-        <v>506375.3025477581</v>
+        <v>-261190.1431614902</v>
       </c>
       <c r="F10" t="n">
-        <v>-66683.54175457833</v>
+        <v>-87695.01850212444</v>
       </c>
       <c r="G10" t="n">
-        <v>447129.3085321696</v>
+        <v>43457.91537323071</v>
       </c>
       <c r="H10" t="n">
-        <v>118747.5225681235</v>
+        <v>26013.581541615</v>
       </c>
       <c r="I10" t="n">
-        <v>-60436.14109309304</v>
+        <v>-60452.69471335109</v>
       </c>
       <c r="J10" t="n">
-        <v>90172.34671979328</v>
+        <v>27098.66801821436</v>
       </c>
       <c r="K10" t="n">
-        <v>-541018.7640233875</v>
+        <v>-817130.9694841735</v>
       </c>
     </row>
     <row r="11">
@@ -848,31 +848,31 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1954</v>
+        <v>1959</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="E11" t="n">
-        <v>-949219.2257644953</v>
+        <v>-533364.4879073185</v>
       </c>
       <c r="F11" t="n">
-        <v>-397424.995404091</v>
+        <v>-121227.3093631855</v>
       </c>
       <c r="G11" t="n">
-        <v>69194.70938540412</v>
+        <v>49002.14097130704</v>
       </c>
       <c r="H11" t="n">
-        <v>27465.75241371982</v>
+        <v>13970.17733040295</v>
       </c>
       <c r="I11" t="n">
-        <v>-253446.0568574639</v>
+        <v>-66742.57418547515</v>
       </c>
       <c r="J11" t="n">
-        <v>116778.6128387377</v>
+        <v>27551.44640890929</v>
       </c>
       <c r="K11" t="n">
-        <v>-1490237.989787883</v>
+        <v>-1350495.457391492</v>
       </c>
     </row>
     <row r="12">
@@ -887,31 +887,31 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1955</v>
+        <v>1960</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="E12" t="n">
-        <v>-788921.0151448989</v>
+        <v>-610961.3393017793</v>
       </c>
       <c r="F12" t="n">
-        <v>-243557.0887063384</v>
+        <v>-101082.175096435</v>
       </c>
       <c r="G12" t="n">
-        <v>55521.814086759</v>
+        <v>47918.80225177216</v>
       </c>
       <c r="H12" t="n">
-        <v>19432.63493036563</v>
+        <v>13277.31410058108</v>
       </c>
       <c r="I12" t="n">
-        <v>-194874.7399738863</v>
+        <v>-79370.69796698864</v>
       </c>
       <c r="J12" t="n">
-        <v>77269.57538082889</v>
+        <v>27922.21054615709</v>
       </c>
       <c r="K12" t="n">
-        <v>-2279159.004932782</v>
+        <v>-1961456.796693271</v>
       </c>
     </row>
     <row r="13">
@@ -926,31 +926,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1956</v>
+        <v>1961</v>
       </c>
       <c r="D13" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="E13" t="n">
-        <v>17969.73935452166</v>
+        <v>-194065.9396997092</v>
       </c>
       <c r="F13" t="n">
-        <v>-79980.48923367087</v>
+        <v>-239367.8415297802</v>
       </c>
       <c r="G13" t="n">
-        <v>179500.063736673</v>
+        <v>135697.1125785473</v>
       </c>
       <c r="H13" t="n">
-        <v>65915.8057596599</v>
+        <v>22352.06617023172</v>
       </c>
       <c r="I13" t="n">
-        <v>-56983.32526233597</v>
+        <v>-37406.07864273011</v>
       </c>
       <c r="J13" t="n">
-        <v>54603.07237641927</v>
+        <v>41979.62583067899</v>
       </c>
       <c r="K13" t="n">
-        <v>-2261189.26557826</v>
+        <v>-2155522.736392981</v>
       </c>
     </row>
     <row r="14">
@@ -965,31 +965,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1957</v>
+        <v>1962</v>
       </c>
       <c r="D14" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E14" t="n">
-        <v>62206.23974094738</v>
+        <v>212605.3093471835</v>
       </c>
       <c r="F14" t="n">
-        <v>-66360.62687547404</v>
+        <v>-80836.993589982</v>
       </c>
       <c r="G14" t="n">
-        <v>102128.4638176654</v>
+        <v>47622.92135147468</v>
       </c>
       <c r="H14" t="n">
-        <v>67576.50652741085</v>
+        <v>29208.16012748254</v>
       </c>
       <c r="I14" t="n">
-        <v>-37312.2467271467</v>
+        <v>-8149.698311011493</v>
       </c>
       <c r="J14" t="n">
-        <v>32401.25099019267</v>
+        <v>18309.69464366246</v>
       </c>
       <c r="K14" t="n">
-        <v>-2198983.025837313</v>
+        <v>-1942917.427045797</v>
       </c>
     </row>
     <row r="15">
@@ -1004,31 +1004,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1958</v>
+        <v>1963</v>
       </c>
       <c r="D15" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="E15" t="n">
-        <v>-262225.3217883687</v>
+        <v>560750.7246843165</v>
       </c>
       <c r="F15" t="n">
-        <v>-88524.63582012538</v>
+        <v>-47207.40755817867</v>
       </c>
       <c r="G15" t="n">
-        <v>44290.93123249937</v>
+        <v>196209.6803994107</v>
       </c>
       <c r="H15" t="n">
-        <v>26013.581541615</v>
+        <v>64004.74236020842</v>
       </c>
       <c r="I15" t="n">
-        <v>-60452.69471335109</v>
+        <v>-6089.142503136506</v>
       </c>
       <c r="J15" t="n">
-        <v>27240.48969879599</v>
+        <v>34553.43843812115</v>
       </c>
       <c r="K15" t="n">
-        <v>-2461208.347625682</v>
+        <v>-1382166.702361481</v>
       </c>
     </row>
     <row r="16">
@@ -1043,31 +1043,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1959</v>
+        <v>1964</v>
       </c>
       <c r="D16" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E16" t="n">
-        <v>-536587.3083902394</v>
+        <v>-754305.3223844708</v>
       </c>
       <c r="F16" t="n">
-        <v>-124572.3550288179</v>
+        <v>-97229.27377711196</v>
       </c>
       <c r="G16" t="n">
-        <v>50419.40388955868</v>
+        <v>79923.39865080231</v>
       </c>
       <c r="H16" t="n">
-        <v>13970.17733040295</v>
+        <v>4275.282339736288</v>
       </c>
       <c r="I16" t="n">
-        <v>-67100.55808259614</v>
+        <v>-55667.97786501707</v>
       </c>
       <c r="J16" t="n">
-        <v>27953.21850416318</v>
+        <v>23961.84366554919</v>
       </c>
       <c r="K16" t="n">
-        <v>-2997795.656015921</v>
+        <v>-2136472.024745951</v>
       </c>
     </row>
     <row r="17">
@@ -1082,31 +1082,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1960</v>
+        <v>1965</v>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E17" t="n">
-        <v>-622916.6327632469</v>
+        <v>261306.4791637006</v>
       </c>
       <c r="F17" t="n">
-        <v>-102253.2726712093</v>
+        <v>-31550.75719409331</v>
       </c>
       <c r="G17" t="n">
-        <v>47918.80225177216</v>
+        <v>50472.27052910699</v>
       </c>
       <c r="H17" t="n">
-        <v>13277.31410058108</v>
+        <v>33138.22222394571</v>
       </c>
       <c r="I17" t="n">
-        <v>-79370.69796698864</v>
+        <v>-18067.86061217749</v>
       </c>
       <c r="J17" t="n">
-        <v>28610.60544965143</v>
+        <v>13945.27294447452</v>
       </c>
       <c r="K17" t="n">
-        <v>-3620712.288779168</v>
+        <v>-1875165.545582251</v>
       </c>
     </row>
     <row r="18">
@@ -1121,31 +1121,31 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1961</v>
+        <v>1966</v>
       </c>
       <c r="D18" t="n">
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
-        <v>-191858.8577856495</v>
+        <v>-403549.988345362</v>
       </c>
       <c r="F18" t="n">
-        <v>-239367.8415297802</v>
+        <v>-70013.10670316906</v>
       </c>
       <c r="G18" t="n">
-        <v>136775.5129755947</v>
+        <v>51340.32005601274</v>
       </c>
       <c r="H18" t="n">
-        <v>22352.06617023172</v>
+        <v>12706.52301717815</v>
       </c>
       <c r="I18" t="n">
-        <v>-37406.07864273011</v>
+        <v>-39897.80950962607</v>
       </c>
       <c r="J18" t="n">
-        <v>42061.67363962285</v>
+        <v>16263.66837453512</v>
       </c>
       <c r="K18" t="n">
-        <v>-3812571.146564818</v>
+        <v>-2278715.533927612</v>
       </c>
     </row>
     <row r="19">
@@ -1160,31 +1160,31 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1962</v>
+        <v>1967</v>
       </c>
       <c r="D19" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="E19" t="n">
-        <v>212068.707573261</v>
+        <v>854062.1701412026</v>
       </c>
       <c r="F19" t="n">
-        <v>-82042.17928475088</v>
+        <v>-38362.77728695045</v>
       </c>
       <c r="G19" t="n">
-        <v>47622.92135147468</v>
+        <v>164237.8234425545</v>
       </c>
       <c r="H19" t="n">
-        <v>29208.16012748254</v>
+        <v>39795.05859283853</v>
       </c>
       <c r="I19" t="n">
-        <v>-8149.698311011493</v>
+        <v>-3612.388616295593</v>
       </c>
       <c r="J19" t="n">
-        <v>18451.74975698932</v>
+        <v>25237.94685701686</v>
       </c>
       <c r="K19" t="n">
-        <v>-3600502.438991556</v>
+        <v>-1424653.36378641</v>
       </c>
     </row>
     <row r="20">
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1963</v>
+        <v>1968</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="E20" t="n">
-        <v>556461.8056198326</v>
+        <v>-61473.30915140099</v>
       </c>
       <c r="F20" t="n">
-        <v>-51496.32662266274</v>
+        <v>-87555.17811621103</v>
       </c>
       <c r="G20" t="n">
-        <v>196209.6803994107</v>
+        <v>142177.9807694448</v>
       </c>
       <c r="H20" t="n">
-        <v>64004.74236020842</v>
+        <v>18508.35819052198</v>
       </c>
       <c r="I20" t="n">
-        <v>-6089.142503136506</v>
+        <v>-16590.00078482607</v>
       </c>
       <c r="J20" t="n">
-        <v>34722.6481138647</v>
+        <v>21375.82760162025</v>
       </c>
       <c r="K20" t="n">
-        <v>-3044040.633371724</v>
+        <v>-1486126.672937811</v>
       </c>
     </row>
     <row r="21">
@@ -1238,31 +1238,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1964</v>
+        <v>1969</v>
       </c>
       <c r="D21" t="n">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="E21" t="n">
-        <v>-755130.1145122561</v>
+        <v>534350.0473078875</v>
       </c>
       <c r="F21" t="n">
-        <v>-97229.27377711196</v>
+        <v>-23574.30649183296</v>
       </c>
       <c r="G21" t="n">
-        <v>79923.39865080231</v>
+        <v>114161.171880272</v>
       </c>
       <c r="H21" t="n">
-        <v>4275.282339736288</v>
+        <v>18584.29070114005</v>
       </c>
       <c r="I21" t="n">
-        <v>-55667.97786501707</v>
+        <v>-5076.115009634558</v>
       </c>
       <c r="J21" t="n">
-        <v>23960.96785786439</v>
+        <v>16354.32447325179</v>
       </c>
       <c r="K21" t="n">
-        <v>-3799170.74788398</v>
+        <v>-951776.6256299234</v>
       </c>
     </row>
     <row r="22">
@@ -1277,31 +1277,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1965</v>
+        <v>1970</v>
       </c>
       <c r="D22" t="n">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E22" t="n">
-        <v>262296.2297170431</v>
+        <v>-290872.7876637541</v>
       </c>
       <c r="F22" t="n">
-        <v>-31550.75719409331</v>
+        <v>-99985.82647633167</v>
       </c>
       <c r="G22" t="n">
-        <v>50472.27052910699</v>
+        <v>48535.93385162025</v>
       </c>
       <c r="H22" t="n">
-        <v>33138.22222394571</v>
+        <v>4548.547534138555</v>
       </c>
       <c r="I22" t="n">
-        <v>-18067.86061217749</v>
+        <v>-22349.11477658377</v>
       </c>
       <c r="J22" t="n">
-        <v>13955.58773060602</v>
+        <v>14881.46110377259</v>
       </c>
       <c r="K22" t="n">
-        <v>-3536874.518166937</v>
+        <v>-1242649.413293677</v>
       </c>
     </row>
     <row r="23">
@@ -1316,31 +1316,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1966</v>
+        <v>1971</v>
       </c>
       <c r="D23" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="E23" t="n">
-        <v>-407344.0321331748</v>
+        <v>-109829.2669632039</v>
       </c>
       <c r="F23" t="n">
-        <v>-70013.10670316906</v>
+        <v>-53372.02934413319</v>
       </c>
       <c r="G23" t="n">
-        <v>51340.32005601274</v>
+        <v>130892.9949876407</v>
       </c>
       <c r="H23" t="n">
-        <v>12706.52301717815</v>
+        <v>6326.453307987994</v>
       </c>
       <c r="I23" t="n">
-        <v>-39897.80950962607</v>
+        <v>-15314.68727555853</v>
       </c>
       <c r="J23" t="n">
-        <v>16422.01535969872</v>
+        <v>17431.32647415586</v>
       </c>
       <c r="K23" t="n">
-        <v>-3944218.550300112</v>
+        <v>-1352478.680256881</v>
       </c>
     </row>
     <row r="24">
@@ -1355,31 +1355,31 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1967</v>
+        <v>1972</v>
       </c>
       <c r="D24" t="n">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="E24" t="n">
-        <v>855324.9165333316</v>
+        <v>-601420.7458716511</v>
       </c>
       <c r="F24" t="n">
-        <v>-38362.77728695045</v>
+        <v>-127776.4951069827</v>
       </c>
       <c r="G24" t="n">
-        <v>164237.8234425545</v>
+        <v>43443.1153805482</v>
       </c>
       <c r="H24" t="n">
-        <v>40255.107188828</v>
+        <v>9999.872922647493</v>
       </c>
       <c r="I24" t="n">
-        <v>-3612.388616295593</v>
+        <v>-30772.47846319065</v>
       </c>
       <c r="J24" t="n">
-        <v>25248.90370882743</v>
+        <v>20139.80603127874</v>
       </c>
       <c r="K24" t="n">
-        <v>-3088893.63376678</v>
+        <v>-1953899.426128532</v>
       </c>
     </row>
     <row r="25">
@@ -1394,31 +1394,31 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1968</v>
+        <v>1973</v>
       </c>
       <c r="D25" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="E25" t="n">
-        <v>-61837.26474677944</v>
+        <v>887127.5956361394</v>
       </c>
       <c r="F25" t="n">
-        <v>-89376.75743949914</v>
+        <v>-26651.79483044438</v>
       </c>
       <c r="G25" t="n">
-        <v>142177.9807694448</v>
+        <v>87084.48367789979</v>
       </c>
       <c r="H25" t="n">
-        <v>19747.33835924522</v>
+        <v>55753.61558028935</v>
       </c>
       <c r="I25" t="n">
-        <v>-16590.00078482607</v>
+        <v>-4838.456623835814</v>
       </c>
       <c r="J25" t="n">
-        <v>21490.02891808737</v>
+        <v>18368.19321154888</v>
       </c>
       <c r="K25" t="n">
-        <v>-3150730.898513559</v>
+        <v>-1066771.830492393</v>
       </c>
     </row>
     <row r="26">
@@ -1433,31 +1433,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1969</v>
+        <v>1974</v>
       </c>
       <c r="D26" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="E26" t="n">
-        <v>538050.3818625627</v>
+        <v>327254.7639933706</v>
       </c>
       <c r="F26" t="n">
-        <v>-23574.30649183296</v>
+        <v>-46879.3386129902</v>
       </c>
       <c r="G26" t="n">
-        <v>114161.171880272</v>
+        <v>53152.68004540823</v>
       </c>
       <c r="H26" t="n">
-        <v>18584.29070114005</v>
+        <v>20838.60216865294</v>
       </c>
       <c r="I26" t="n">
-        <v>-5076.115009634558</v>
+        <v>-5199.445082419644</v>
       </c>
       <c r="J26" t="n">
-        <v>16474.11522234856</v>
+        <v>10947.13491328346</v>
       </c>
       <c r="K26" t="n">
-        <v>-2612680.516650997</v>
+        <v>-739517.0664990223</v>
       </c>
     </row>
     <row r="27">
@@ -1472,31 +1472,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1970</v>
+        <v>1975</v>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="E27" t="n">
-        <v>-293685.1200699247</v>
+        <v>-203279.1915665647</v>
       </c>
       <c r="F27" t="n">
-        <v>-99985.82647633167</v>
+        <v>-58192.68398835488</v>
       </c>
       <c r="G27" t="n">
-        <v>48535.93385162025</v>
+        <v>17935.68385679433</v>
       </c>
       <c r="H27" t="n">
-        <v>4548.547534138555</v>
+        <v>6558.120356825486</v>
       </c>
       <c r="I27" t="n">
-        <v>-22930.69340712635</v>
+        <v>-13425.84076860084</v>
       </c>
       <c r="J27" t="n">
-        <v>14933.82519248119</v>
+        <v>7905.691273235028</v>
       </c>
       <c r="K27" t="n">
-        <v>-2906365.636720921</v>
+        <v>-942796.258065587</v>
       </c>
     </row>
     <row r="28">
@@ -1511,31 +1511,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1971</v>
+        <v>1976</v>
       </c>
       <c r="D28" t="n">
-        <v>80</v>
+        <v>126</v>
       </c>
       <c r="E28" t="n">
-        <v>-109911.5037560125</v>
+        <v>-1235950.013560917</v>
       </c>
       <c r="F28" t="n">
-        <v>-53372.02934413319</v>
+        <v>-68107.18351949868</v>
       </c>
       <c r="G28" t="n">
-        <v>130892.9949876407</v>
+        <v>10462.48224979667</v>
       </c>
       <c r="H28" t="n">
-        <v>6326.453307987994</v>
+        <v>1438.340388237656</v>
       </c>
       <c r="I28" t="n">
-        <v>-15314.68727555853</v>
+        <v>-40537.47812120829</v>
       </c>
       <c r="J28" t="n">
-        <v>17434.40565957254</v>
+        <v>12529.92874581502</v>
       </c>
       <c r="K28" t="n">
-        <v>-3016277.140476934</v>
+        <v>-2178746.271626504</v>
       </c>
     </row>
     <row r="29">
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1972</v>
+        <v>1977</v>
       </c>
       <c r="D29" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="E29" t="n">
-        <v>-601526.1265760472</v>
+        <v>-1059468.362487814</v>
       </c>
       <c r="F29" t="n">
-        <v>-127776.4951069827</v>
+        <v>-118076.5853905626</v>
       </c>
       <c r="G29" t="n">
-        <v>43443.1153805482</v>
+        <v>23555.5658066434</v>
       </c>
       <c r="H29" t="n">
-        <v>9999.872922647493</v>
+        <v>6624.838358979776</v>
       </c>
       <c r="I29" t="n">
-        <v>-30772.47846319065</v>
+        <v>-28799.56111095283</v>
       </c>
       <c r="J29" t="n">
-        <v>20140.38054183823</v>
+        <v>14894.50010556251</v>
       </c>
       <c r="K29" t="n">
-        <v>-3617803.267052981</v>
+        <v>-3238214.634114318</v>
       </c>
     </row>
     <row r="30">
@@ -1589,31 +1589,31 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1973</v>
+        <v>1978</v>
       </c>
       <c r="D30" t="n">
-        <v>91</v>
+        <v>133</v>
       </c>
       <c r="E30" t="n">
-        <v>887532.5216626027</v>
+        <v>1349043.923302277</v>
       </c>
       <c r="F30" t="n">
-        <v>-26651.79483044438</v>
+        <v>-89377.15540855493</v>
       </c>
       <c r="G30" t="n">
-        <v>87084.48367789979</v>
+        <v>73468.19984877533</v>
       </c>
       <c r="H30" t="n">
-        <v>55753.61558028935</v>
+        <v>38713.59980996651</v>
       </c>
       <c r="I30" t="n">
-        <v>-4838.456623835814</v>
+        <v>-3182.821254536498</v>
       </c>
       <c r="J30" t="n">
-        <v>18377.93716964563</v>
+        <v>16009.45416661273</v>
       </c>
       <c r="K30" t="n">
-        <v>-2730270.745390378</v>
+        <v>-1889170.710812041</v>
       </c>
     </row>
     <row r="31">
@@ -1628,31 +1628,31 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1974</v>
+        <v>1979</v>
       </c>
       <c r="D31" t="n">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="E31" t="n">
-        <v>328429.7322968545</v>
+        <v>402096.2579257016</v>
       </c>
       <c r="F31" t="n">
-        <v>-46879.3386129902</v>
+        <v>-9254.903120204011</v>
       </c>
       <c r="G31" t="n">
-        <v>53152.68004540823</v>
+        <v>94262.54395442427</v>
       </c>
       <c r="H31" t="n">
-        <v>21207.25512693744</v>
+        <v>11687.79596391124</v>
       </c>
       <c r="I31" t="n">
-        <v>-5199.445082419644</v>
+        <v>-5444.668237210794</v>
       </c>
       <c r="J31" t="n">
-        <v>10959.35881048397</v>
+        <v>10715.97559736954</v>
       </c>
       <c r="K31" t="n">
-        <v>-2401841.013093524</v>
+        <v>-1487074.45288634</v>
       </c>
     </row>
     <row r="32">
@@ -1667,31 +1667,31 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1975</v>
+        <v>1980</v>
       </c>
       <c r="D32" t="n">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="E32" t="n">
-        <v>-203481.5897051115</v>
+        <v>501191.3332129866</v>
       </c>
       <c r="F32" t="n">
-        <v>-58192.68398835488</v>
+        <v>-57944.91154203418</v>
       </c>
       <c r="G32" t="n">
-        <v>17935.68385679433</v>
+        <v>37655.6351946103</v>
       </c>
       <c r="H32" t="n">
-        <v>6558.120356825486</v>
+        <v>19038.41878417934</v>
       </c>
       <c r="I32" t="n">
-        <v>-13425.84076860084</v>
+        <v>-4682.231417861639</v>
       </c>
       <c r="J32" t="n">
-        <v>7908.201709105521</v>
+        <v>8759.921829965508</v>
       </c>
       <c r="K32" t="n">
-        <v>-2605322.602798635</v>
+        <v>-985883.1196733529</v>
       </c>
     </row>
     <row r="33">
@@ -1706,31 +1706,31 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1976</v>
+        <v>1981</v>
       </c>
       <c r="D33" t="n">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="E33" t="n">
-        <v>-1236243.537078917</v>
+        <v>-34893.97929250308</v>
       </c>
       <c r="F33" t="n">
-        <v>-68107.18351949868</v>
+        <v>-30024.24966305032</v>
       </c>
       <c r="G33" t="n">
-        <v>10462.48224979667</v>
+        <v>61860.10826784731</v>
       </c>
       <c r="H33" t="n">
-        <v>1527.863318920519</v>
+        <v>8680.443047276169</v>
       </c>
       <c r="I33" t="n">
-        <v>-40537.47812120829</v>
+        <v>-12064.2178136835</v>
       </c>
       <c r="J33" t="n">
-        <v>12529.14251139893</v>
+        <v>8415.516547195621</v>
       </c>
       <c r="K33" t="n">
-        <v>-3841566.139877553</v>
+        <v>-1020777.098965856</v>
       </c>
     </row>
     <row r="34">
@@ -1745,31 +1745,31 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1977</v>
+        <v>1982</v>
       </c>
       <c r="D34" t="n">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="E34" t="n">
-        <v>-1063743.123459339</v>
+        <v>1012708.366725947</v>
       </c>
       <c r="F34" t="n">
-        <v>-118076.5853905626</v>
+        <v>-8911.713583529217</v>
       </c>
       <c r="G34" t="n">
-        <v>23555.5658066434</v>
+        <v>89542.19386511837</v>
       </c>
       <c r="H34" t="n">
-        <v>6624.838358979776</v>
+        <v>28242.46997817886</v>
       </c>
       <c r="I34" t="n">
-        <v>-28799.56111095283</v>
+        <v>-1463.299148270188</v>
       </c>
       <c r="J34" t="n">
-        <v>14960.5113616036</v>
+        <v>11003.3143448302</v>
       </c>
       <c r="K34" t="n">
-        <v>-4905309.263336892</v>
+        <v>-8068.732239909004</v>
       </c>
     </row>
     <row r="35">
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1978</v>
+        <v>1983</v>
       </c>
       <c r="D35" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="E35" t="n">
-        <v>1353521.260352391</v>
+        <v>570520.5256889896</v>
       </c>
       <c r="F35" t="n">
-        <v>-89377.15540855493</v>
+        <v>-133972.2021201176</v>
       </c>
       <c r="G35" t="n">
-        <v>73468.19984877533</v>
+        <v>69944.00048925159</v>
       </c>
       <c r="H35" t="n">
-        <v>38713.59980996651</v>
+        <v>24128.96978795599</v>
       </c>
       <c r="I35" t="n">
-        <v>-3182.821254536498</v>
+        <v>-5427.818022625609</v>
       </c>
       <c r="J35" t="n">
-        <v>16060.84106565679</v>
+        <v>16725.19125071759</v>
       </c>
       <c r="K35" t="n">
-        <v>-3551788.002984501</v>
+        <v>562451.7934490805</v>
       </c>
     </row>
     <row r="36">
@@ -1823,31 +1823,31 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>1979</v>
+        <v>1984</v>
       </c>
       <c r="D36" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="E36" t="n">
-        <v>402168.0945429113</v>
+        <v>-464688.7943692293</v>
       </c>
       <c r="F36" t="n">
-        <v>-9254.903120204011</v>
+        <v>-79988.805538906</v>
       </c>
       <c r="G36" t="n">
-        <v>94262.54395442427</v>
+        <v>44122.81244586152</v>
       </c>
       <c r="H36" t="n">
-        <v>11687.79596391124</v>
+        <v>4636.577553995554</v>
       </c>
       <c r="I36" t="n">
-        <v>-5444.668237210794</v>
+        <v>-20247.80278370457</v>
       </c>
       <c r="J36" t="n">
-        <v>10715.99152359375</v>
+        <v>12412.50768043667</v>
       </c>
       <c r="K36" t="n">
-        <v>-3149619.90844159</v>
+        <v>97762.9990798512</v>
       </c>
     </row>
     <row r="37">
@@ -1862,31 +1862,31 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1980</v>
+        <v>1985</v>
       </c>
       <c r="D37" t="n">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E37" t="n">
-        <v>500705.9007177303</v>
+        <v>-179181.9279356335</v>
       </c>
       <c r="F37" t="n">
-        <v>-57944.91154203418</v>
+        <v>-46740.99960843119</v>
       </c>
       <c r="G37" t="n">
-        <v>37655.6351946103</v>
+        <v>53560.03074547494</v>
       </c>
       <c r="H37" t="n">
-        <v>19038.41878417934</v>
+        <v>12009.96676889124</v>
       </c>
       <c r="I37" t="n">
-        <v>-4682.231417861639</v>
+        <v>-11368.27633845327</v>
       </c>
       <c r="J37" t="n">
-        <v>8766.899431962611</v>
+        <v>10216.87641450704</v>
       </c>
       <c r="K37" t="n">
-        <v>-2648914.00772386</v>
+        <v>-81418.92885578229</v>
       </c>
     </row>
     <row r="38">
@@ -1901,31 +1901,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>1981</v>
+        <v>1986</v>
       </c>
       <c r="D38" t="n">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E38" t="n">
-        <v>-35846.16538319318</v>
+        <v>435653.7734504882</v>
       </c>
       <c r="F38" t="n">
-        <v>-30024.24966305032</v>
+        <v>-34625.57096076782</v>
       </c>
       <c r="G38" t="n">
-        <v>61860.10826784731</v>
+        <v>115146.1618756205</v>
       </c>
       <c r="H38" t="n">
-        <v>8780.843346019872</v>
+        <v>11733.78162506511</v>
       </c>
       <c r="I38" t="n">
-        <v>-12210.49442220699</v>
+        <v>-2379.958916286665</v>
       </c>
       <c r="J38" t="n">
-        <v>8434.933037460622</v>
+        <v>11198.44025815879</v>
       </c>
       <c r="K38" t="n">
-        <v>-2684760.173107053</v>
+        <v>354234.844594706</v>
       </c>
     </row>
     <row r="39">
@@ -1940,31 +1940,31 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1982</v>
+        <v>1987</v>
       </c>
       <c r="D39" t="n">
         <v>148</v>
       </c>
       <c r="E39" t="n">
-        <v>1018754.576754392</v>
+        <v>-351399.4807462298</v>
       </c>
       <c r="F39" t="n">
-        <v>-8911.713583529217</v>
+        <v>-33912.81103699534</v>
       </c>
       <c r="G39" t="n">
-        <v>89542.19386511837</v>
+        <v>33238.06734553994</v>
       </c>
       <c r="H39" t="n">
-        <v>28242.46997817886</v>
+        <v>2241.724717782637</v>
       </c>
       <c r="I39" t="n">
-        <v>-1463.299148270188</v>
+        <v>-12380.42174700204</v>
       </c>
       <c r="J39" t="n">
-        <v>11056.9110022586</v>
+        <v>5778.080318975388</v>
       </c>
       <c r="K39" t="n">
-        <v>-1666005.596352661</v>
+        <v>2835.363848476205</v>
       </c>
     </row>
     <row r="40">
@@ -1979,31 +1979,31 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1983</v>
+        <v>1988</v>
       </c>
       <c r="D40" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E40" t="n">
-        <v>572442.9731078713</v>
+        <v>-249653.8135055751</v>
       </c>
       <c r="F40" t="n">
-        <v>-133972.2021201176</v>
+        <v>-25136.85726969508</v>
       </c>
       <c r="G40" t="n">
-        <v>69944.00048925159</v>
+        <v>9416.15386406672</v>
       </c>
       <c r="H40" t="n">
-        <v>24128.96978795599</v>
+        <v>5319.174136536445</v>
       </c>
       <c r="I40" t="n">
-        <v>-5427.818022625609</v>
+        <v>-10292.30067587324</v>
       </c>
       <c r="J40" t="n">
-        <v>16727.5520938271</v>
+        <v>5192.867947596095</v>
       </c>
       <c r="K40" t="n">
-        <v>-1093562.623244789</v>
+        <v>-246818.4496570989</v>
       </c>
     </row>
     <row r="41">
@@ -2018,31 +2018,31 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1984</v>
+        <v>1989</v>
       </c>
       <c r="D41" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E41" t="n">
-        <v>-465415.1453857525</v>
+        <v>46965.13747959995</v>
       </c>
       <c r="F41" t="n">
-        <v>-79988.805538906</v>
+        <v>-18759.04760712362</v>
       </c>
       <c r="G41" t="n">
-        <v>44122.81244586152</v>
+        <v>27929.84141077228</v>
       </c>
       <c r="H41" t="n">
-        <v>4636.577553995554</v>
+        <v>10889.17865305919</v>
       </c>
       <c r="I41" t="n">
-        <v>-20247.80278370457</v>
+        <v>-7022.495999547182</v>
       </c>
       <c r="J41" t="n">
-        <v>12412.89950940639</v>
+        <v>5742.301503846003</v>
       </c>
       <c r="K41" t="n">
-        <v>-1558977.768630542</v>
+        <v>-199853.3121774989</v>
       </c>
     </row>
     <row r="42">
@@ -2057,31 +2057,31 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1985</v>
+        <v>1990</v>
       </c>
       <c r="D42" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E42" t="n">
-        <v>-181713.9828432405</v>
+        <v>-1042725.760223119</v>
       </c>
       <c r="F42" t="n">
-        <v>-46740.99960843119</v>
+        <v>-44592.33410418264</v>
       </c>
       <c r="G42" t="n">
-        <v>53560.03074547494</v>
+        <v>17540.50037842964</v>
       </c>
       <c r="H42" t="n">
-        <v>12009.96676889124</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>-11368.27633845327</v>
+        <v>-18881.77040756936</v>
       </c>
       <c r="J42" t="n">
-        <v>10255.6183307797</v>
+        <v>7640.454103673275</v>
       </c>
       <c r="K42" t="n">
-        <v>-1740691.751473782</v>
+        <v>-1242579.072400618</v>
       </c>
     </row>
     <row r="43">
@@ -2096,31 +2096,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1986</v>
+        <v>1991</v>
       </c>
       <c r="D43" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="E43" t="n">
-        <v>436400.5845862557</v>
+        <v>-917707.1463274964</v>
       </c>
       <c r="F43" t="n">
-        <v>-34625.57096076782</v>
+        <v>-139336.3134025569</v>
       </c>
       <c r="G43" t="n">
-        <v>115146.1618756205</v>
+        <v>44130.14854250991</v>
       </c>
       <c r="H43" t="n">
-        <v>11733.78162506511</v>
+        <v>7683.340241129192</v>
       </c>
       <c r="I43" t="n">
-        <v>-2379.958916286665</v>
+        <v>-36748.41267105583</v>
       </c>
       <c r="J43" t="n">
-        <v>11201.09079434966</v>
+        <v>19271.67860400483</v>
       </c>
       <c r="K43" t="n">
-        <v>-1304291.166887527</v>
+        <v>-2160286.218728114</v>
       </c>
     </row>
     <row r="44">
@@ -2135,31 +2135,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>1987</v>
+        <v>1992</v>
       </c>
       <c r="D44" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="E44" t="n">
-        <v>-352032.4683578571</v>
+        <v>44649.05789432273</v>
       </c>
       <c r="F44" t="n">
-        <v>-33912.81103699534</v>
+        <v>-298442.7677549825</v>
       </c>
       <c r="G44" t="n">
-        <v>33238.06734553994</v>
+        <v>204106.9205945327</v>
       </c>
       <c r="H44" t="n">
-        <v>2241.724717782637</v>
+        <v>23147.99170610888</v>
       </c>
       <c r="I44" t="n">
-        <v>-12380.42174700204</v>
+        <v>-11553.7452218598</v>
       </c>
       <c r="J44" t="n">
-        <v>5779.212728544972</v>
+        <v>32529.64949480723</v>
       </c>
       <c r="K44" t="n">
-        <v>-1656323.635245384</v>
+        <v>-2115637.160833792</v>
       </c>
     </row>
     <row r="45">
@@ -2174,31 +2174,31 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1988</v>
+        <v>1993</v>
       </c>
       <c r="D45" t="n">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="E45" t="n">
-        <v>-250966.6117455783</v>
+        <v>1248702.537801742</v>
       </c>
       <c r="F45" t="n">
-        <v>-25136.85726969508</v>
+        <v>-36112.20397486133</v>
       </c>
       <c r="G45" t="n">
-        <v>9416.15386406672</v>
+        <v>83036.73868831829</v>
       </c>
       <c r="H45" t="n">
-        <v>5319.174136536445</v>
+        <v>29718.35419390804</v>
       </c>
       <c r="I45" t="n">
-        <v>-10292.30067587324</v>
+        <v>-1698.057720661953</v>
       </c>
       <c r="J45" t="n">
-        <v>5202.717687843934</v>
+        <v>13230.23087030574</v>
       </c>
       <c r="K45" t="n">
-        <v>-1907290.246990962</v>
+        <v>-866934.6230320497</v>
       </c>
     </row>
     <row r="46">
@@ -2213,31 +2213,31 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>1989</v>
+        <v>1994</v>
       </c>
       <c r="D46" t="n">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="E46" t="n">
-        <v>48918.90019617826</v>
+        <v>-1509638.863229874</v>
       </c>
       <c r="F46" t="n">
-        <v>-18759.04760712362</v>
+        <v>-415571.4037174825</v>
       </c>
       <c r="G46" t="n">
-        <v>27929.84141077228</v>
+        <v>23811.21107651855</v>
       </c>
       <c r="H46" t="n">
-        <v>10889.17865305919</v>
+        <v>1110.699226202805</v>
       </c>
       <c r="I46" t="n">
-        <v>-7022.495999547182</v>
+        <v>-26518.40947637214</v>
       </c>
       <c r="J46" t="n">
-        <v>5759.961587613613</v>
+        <v>33512.56834442584</v>
       </c>
       <c r="K46" t="n">
-        <v>-1858371.346794784</v>
+        <v>-2376573.486261923</v>
       </c>
     </row>
     <row r="47">
@@ -2252,31 +2252,31 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1990</v>
+        <v>1995</v>
       </c>
       <c r="D47" t="n">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="E47" t="n">
-        <v>-1046469.671767358</v>
+        <v>1833565.595110081</v>
       </c>
       <c r="F47" t="n">
-        <v>-44592.33410418264</v>
+        <v>-63084.35900603847</v>
       </c>
       <c r="G47" t="n">
-        <v>17540.50037842964</v>
+        <v>399526.0399679262</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>30596.07480875194</v>
       </c>
       <c r="I47" t="n">
-        <v>-18881.77040756936</v>
+        <v>-4315.656422549044</v>
       </c>
       <c r="J47" t="n">
-        <v>7667.983955673876</v>
+        <v>39613.07026966738</v>
       </c>
       <c r="K47" t="n">
-        <v>-2904841.018562142</v>
+        <v>-543007.8911518422</v>
       </c>
     </row>
     <row r="48">
@@ -2291,31 +2291,31 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>1991</v>
+        <v>1996</v>
       </c>
       <c r="D48" t="n">
-        <v>133</v>
+        <v>190</v>
       </c>
       <c r="E48" t="n">
-        <v>-922728.7794908122</v>
+        <v>-76851.10586987232</v>
       </c>
       <c r="F48" t="n">
-        <v>-139336.3134025569</v>
+        <v>-257800.361465252</v>
       </c>
       <c r="G48" t="n">
-        <v>44130.14854250991</v>
+        <v>32717.13728731511</v>
       </c>
       <c r="H48" t="n">
-        <v>7683.340241129192</v>
+        <v>12245.11445847984</v>
       </c>
       <c r="I48" t="n">
-        <v>-39045.05138660107</v>
+        <v>-6983.313692125844</v>
       </c>
       <c r="J48" t="n">
-        <v>19318.45254955298</v>
+        <v>20441.59650325945</v>
       </c>
       <c r="K48" t="n">
-        <v>-3827569.798052954</v>
+        <v>-619858.9970217145</v>
       </c>
     </row>
     <row r="49">
@@ -2330,31 +2330,31 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1992</v>
+        <v>1997</v>
       </c>
       <c r="D49" t="n">
-        <v>140</v>
+        <v>178</v>
       </c>
       <c r="E49" t="n">
-        <v>52714.1040805282</v>
+        <v>-28905.07693039486</v>
       </c>
       <c r="F49" t="n">
-        <v>-298442.7677549825</v>
+        <v>-36514.13941000673</v>
       </c>
       <c r="G49" t="n">
-        <v>204106.9205945327</v>
+        <v>36503.87066079754</v>
       </c>
       <c r="H49" t="n">
-        <v>23227.60648142067</v>
+        <v>5819.533648693126</v>
       </c>
       <c r="I49" t="n">
-        <v>-11553.7452218598</v>
+        <v>-8484.886492621663</v>
       </c>
       <c r="J49" t="n">
-        <v>32590.10358932364</v>
+        <v>6839.995587427585</v>
       </c>
       <c r="K49" t="n">
-        <v>-3774855.693972426</v>
+        <v>-648764.0739521093</v>
       </c>
     </row>
     <row r="50">
@@ -2369,31 +2369,31 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1993</v>
+        <v>1998</v>
       </c>
       <c r="D50" t="n">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E50" t="n">
-        <v>1253845.436417434</v>
+        <v>682588.5240309548</v>
       </c>
       <c r="F50" t="n">
-        <v>-36112.20397486133</v>
+        <v>-34897.82735342336</v>
       </c>
       <c r="G50" t="n">
-        <v>83036.73868831829</v>
+        <v>70999.61767373206</v>
       </c>
       <c r="H50" t="n">
-        <v>29718.35419390804</v>
+        <v>17708.28322321636</v>
       </c>
       <c r="I50" t="n">
-        <v>-1698.057720661953</v>
+        <v>-6691.615674443996</v>
       </c>
       <c r="J50" t="n">
-        <v>13259.13569121398</v>
+        <v>9607.240260501745</v>
       </c>
       <c r="K50" t="n">
-        <v>-2521010.257554992</v>
+        <v>33824.45007884549</v>
       </c>
     </row>
     <row r="51">
@@ -2408,31 +2408,31 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1994</v>
+        <v>1999</v>
       </c>
       <c r="D51" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E51" t="n">
-        <v>-1510691.907547294</v>
+        <v>-473640.9874491059</v>
       </c>
       <c r="F51" t="n">
-        <v>-415571.4037174825</v>
+        <v>-49561.8009574188</v>
       </c>
       <c r="G51" t="n">
-        <v>23811.21107651855</v>
+        <v>139491.9172930275</v>
       </c>
       <c r="H51" t="n">
-        <v>1110.699226202805</v>
+        <v>4559.094316121606</v>
       </c>
       <c r="I51" t="n">
-        <v>-26518.40947637214</v>
+        <v>-19670.69765093717</v>
       </c>
       <c r="J51" t="n">
-        <v>33511.79467344124</v>
+        <v>13717.31555422262</v>
       </c>
       <c r="K51" t="n">
-        <v>-4031702.165102286</v>
+        <v>-439816.5373702605</v>
       </c>
     </row>
     <row r="52">
@@ -2447,31 +2447,31 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>1995</v>
+        <v>2000</v>
       </c>
       <c r="D52" t="n">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="E52" t="n">
-        <v>1832935.351281118</v>
+        <v>-143957.7151852404</v>
       </c>
       <c r="F52" t="n">
-        <v>-63084.35900603847</v>
+        <v>-153816.2706580816</v>
       </c>
       <c r="G52" t="n">
-        <v>399526.0399679262</v>
+        <v>174767.9308244124</v>
       </c>
       <c r="H52" t="n">
-        <v>30596.07480875194</v>
+        <v>8085.444891304371</v>
       </c>
       <c r="I52" t="n">
-        <v>-4315.656422549044</v>
+        <v>-11615.96760870518</v>
       </c>
       <c r="J52" t="n">
-        <v>39619.18412300513</v>
+        <v>20447.81849327552</v>
       </c>
       <c r="K52" t="n">
-        <v>-2198766.813821169</v>
+        <v>-583774.2525555009</v>
       </c>
     </row>
     <row r="53">
@@ -2486,31 +2486,31 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>1996</v>
+        <v>2001</v>
       </c>
       <c r="D53" t="n">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="E53" t="n">
-        <v>-75677.80611507106</v>
+        <v>-860488.4456229911</v>
       </c>
       <c r="F53" t="n">
-        <v>-257800.361465252</v>
+        <v>-154166.537534851</v>
       </c>
       <c r="G53" t="n">
-        <v>32717.13728731511</v>
+        <v>35217.5535153194</v>
       </c>
       <c r="H53" t="n">
-        <v>12245.11445847984</v>
+        <v>2927.706636349355</v>
       </c>
       <c r="I53" t="n">
-        <v>-6983.313692125844</v>
+        <v>-20727.98342839225</v>
       </c>
       <c r="J53" t="n">
-        <v>20446.3030113888</v>
+        <v>15186.19421180417</v>
       </c>
       <c r="K53" t="n">
-        <v>-2274444.61993624</v>
+        <v>-1444262.698178492</v>
       </c>
     </row>
     <row r="54">
@@ -2525,31 +2525,31 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="D54" t="n">
-        <v>178</v>
+        <v>243</v>
       </c>
       <c r="E54" t="n">
-        <v>-28378.1775745083</v>
+        <v>-72434.54453102907</v>
       </c>
       <c r="F54" t="n">
-        <v>-36514.13941000673</v>
+        <v>-57040.00698760246</v>
       </c>
       <c r="G54" t="n">
-        <v>36503.87066079754</v>
+        <v>61968.85786399541</v>
       </c>
       <c r="H54" t="n">
-        <v>5987.245954209967</v>
+        <v>8841.170406313207</v>
       </c>
       <c r="I54" t="n">
-        <v>-8484.886492621663</v>
+        <v>-10954.13094414511</v>
       </c>
       <c r="J54" t="n">
-        <v>6847.535372461425</v>
+        <v>8198.870501615009</v>
       </c>
       <c r="K54" t="n">
-        <v>-2302822.797510748</v>
+        <v>-1516697.242709521</v>
       </c>
     </row>
     <row r="55">
@@ -2564,31 +2564,31 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="D55" t="n">
-        <v>154</v>
+        <v>257</v>
       </c>
       <c r="E55" t="n">
-        <v>687792.699469539</v>
+        <v>592722.6308151548</v>
       </c>
       <c r="F55" t="n">
-        <v>-34897.82735342336</v>
+        <v>-30404.5084277621</v>
       </c>
       <c r="G55" t="n">
-        <v>70999.61767373206</v>
+        <v>40024.4411170633</v>
       </c>
       <c r="H55" t="n">
-        <v>17990.71430390289</v>
+        <v>10035.94647547538</v>
       </c>
       <c r="I55" t="n">
-        <v>-6691.615674443996</v>
+        <v>-2220.658935643182</v>
       </c>
       <c r="J55" t="n">
-        <v>9656.797387810873</v>
+        <v>5575.071039209531</v>
       </c>
       <c r="K55" t="n">
-        <v>-1615030.098041209</v>
+        <v>-923974.6118943664</v>
       </c>
     </row>
     <row r="56">
@@ -2603,31 +2603,31 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1999</v>
+        <v>2004</v>
       </c>
       <c r="D56" t="n">
-        <v>167</v>
+        <v>256</v>
       </c>
       <c r="E56" t="n">
-        <v>-479128.4176849455</v>
+        <v>28692.09713651087</v>
       </c>
       <c r="F56" t="n">
-        <v>-49561.8009574188</v>
+        <v>-52579.40386784749</v>
       </c>
       <c r="G56" t="n">
-        <v>139491.9172930275</v>
+        <v>53012.82047737976</v>
       </c>
       <c r="H56" t="n">
-        <v>4559.094316121606</v>
+        <v>5936.160450501784</v>
       </c>
       <c r="I56" t="n">
-        <v>-19670.69765093717</v>
+        <v>-7343.366909323999</v>
       </c>
       <c r="J56" t="n">
-        <v>13749.30146653106</v>
+        <v>7224.750902925433</v>
       </c>
       <c r="K56" t="n">
-        <v>-2094158.515726155</v>
+        <v>-895282.5147578556</v>
       </c>
     </row>
     <row r="57">
@@ -2642,31 +2642,31 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2000</v>
+        <v>2005</v>
       </c>
       <c r="D57" t="n">
-        <v>154</v>
+        <v>265</v>
       </c>
       <c r="E57" t="n">
-        <v>-144767.7125543424</v>
+        <v>207316.9441999972</v>
       </c>
       <c r="F57" t="n">
-        <v>-153816.2706580816</v>
+        <v>-44662.88107333597</v>
       </c>
       <c r="G57" t="n">
-        <v>174767.9308244124</v>
+        <v>65184.82959734288</v>
       </c>
       <c r="H57" t="n">
-        <v>8279.656959573607</v>
+        <v>7184.860099026921</v>
       </c>
       <c r="I57" t="n">
-        <v>-12563.37962166124</v>
+        <v>-3353.586363214618</v>
       </c>
       <c r="J57" t="n">
-        <v>20457.82997111797</v>
+        <v>6637.151928163719</v>
       </c>
       <c r="K57" t="n">
-        <v>-2238926.228280497</v>
+        <v>-687965.5705578583</v>
       </c>
     </row>
     <row r="58">
@@ -2681,31 +2681,31 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>2001</v>
+        <v>2006</v>
       </c>
       <c r="D58" t="n">
-        <v>204</v>
+        <v>276</v>
       </c>
       <c r="E58" t="n">
-        <v>-859236.8999921812</v>
+        <v>394220.5023290247</v>
       </c>
       <c r="F58" t="n">
-        <v>-154166.537534851</v>
+        <v>-18512.80312540646</v>
       </c>
       <c r="G58" t="n">
-        <v>35217.5535153194</v>
+        <v>54452.25976800311</v>
       </c>
       <c r="H58" t="n">
-        <v>3139.666636996561</v>
+        <v>5929.417557970974</v>
       </c>
       <c r="I58" t="n">
-        <v>-20727.98342839225</v>
+        <v>-3991.112390518948</v>
       </c>
       <c r="J58" t="n">
-        <v>15189.84665524728</v>
+        <v>7029.388335099463</v>
       </c>
       <c r="K58" t="n">
-        <v>-3098163.128272679</v>
+        <v>-293745.0682288336</v>
       </c>
     </row>
     <row r="59">
@@ -2720,31 +2720,31 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="D59" t="n">
-        <v>243</v>
+        <v>276</v>
       </c>
       <c r="E59" t="n">
-        <v>-72775.48347167141</v>
+        <v>-692186.1489248393</v>
       </c>
       <c r="F59" t="n">
-        <v>-57040.00698760246</v>
+        <v>-46606.67913512616</v>
       </c>
       <c r="G59" t="n">
-        <v>61968.85786399541</v>
+        <v>19028.26334016675</v>
       </c>
       <c r="H59" t="n">
-        <v>8841.170406313207</v>
+        <v>2609.518904326229</v>
       </c>
       <c r="I59" t="n">
-        <v>-10954.13094414511</v>
+        <v>-12025.35394269675</v>
       </c>
       <c r="J59" t="n">
-        <v>8199.490091790127</v>
+        <v>5897.724734796427</v>
       </c>
       <c r="K59" t="n">
-        <v>-3170938.61174435</v>
+        <v>-985931.2171536729</v>
       </c>
     </row>
     <row r="60">
@@ -2759,31 +2759,31 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2003</v>
+        <v>2008</v>
       </c>
       <c r="D60" t="n">
-        <v>257</v>
+        <v>303</v>
       </c>
       <c r="E60" t="n">
-        <v>593233.5445967265</v>
+        <v>-755516.642504215</v>
       </c>
       <c r="F60" t="n">
-        <v>-30404.5084277621</v>
+        <v>-70907.2072196057</v>
       </c>
       <c r="G60" t="n">
-        <v>40024.4411170633</v>
+        <v>21342.95825366138</v>
       </c>
       <c r="H60" t="n">
-        <v>10035.94647547538</v>
+        <v>1161.260446669155</v>
       </c>
       <c r="I60" t="n">
-        <v>-2220.658935643182</v>
+        <v>-10490.97599352949</v>
       </c>
       <c r="J60" t="n">
-        <v>5575.677434403559</v>
+        <v>6222.928355891765</v>
       </c>
       <c r="K60" t="n">
-        <v>-2577705.067147624</v>
+        <v>-1741447.859657888</v>
       </c>
     </row>
     <row r="61">
@@ -2798,31 +2798,31 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2004</v>
+        <v>2009</v>
       </c>
       <c r="D61" t="n">
-        <v>256</v>
+        <v>317</v>
       </c>
       <c r="E61" t="n">
-        <v>28221.94300677659</v>
+        <v>-548521.0936452624</v>
       </c>
       <c r="F61" t="n">
-        <v>-52579.40386784749</v>
+        <v>-41684.20055600411</v>
       </c>
       <c r="G61" t="n">
-        <v>53012.82047737976</v>
+        <v>52272.25783075261</v>
       </c>
       <c r="H61" t="n">
-        <v>5936.160450501784</v>
+        <v>6384.312051098422</v>
       </c>
       <c r="I61" t="n">
-        <v>-7343.366909323999</v>
+        <v>-12918.18321262167</v>
       </c>
       <c r="J61" t="n">
-        <v>7226.27920159974</v>
+        <v>8751.193416964539</v>
       </c>
       <c r="K61" t="n">
-        <v>-2549483.124140847</v>
+        <v>-2289968.95330315</v>
       </c>
     </row>
     <row r="62">
@@ -2837,31 +2837,31 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2005</v>
+        <v>2010</v>
       </c>
       <c r="D62" t="n">
-        <v>265</v>
+        <v>365</v>
       </c>
       <c r="E62" t="n">
-        <v>209190.2945480003</v>
+        <v>702347.1784507469</v>
       </c>
       <c r="F62" t="n">
-        <v>-44662.88107333597</v>
+        <v>-54248.19948097832</v>
       </c>
       <c r="G62" t="n">
-        <v>65184.82959734288</v>
+        <v>72835.42036691456</v>
       </c>
       <c r="H62" t="n">
-        <v>7265.366456604237</v>
+        <v>9215.49108779008</v>
       </c>
       <c r="I62" t="n">
-        <v>-3353.586363214618</v>
+        <v>-2823.986900952769</v>
       </c>
       <c r="J62" t="n">
-        <v>6645.788386415454</v>
+        <v>6915.435789136386</v>
       </c>
       <c r="K62" t="n">
-        <v>-2340292.829592847</v>
+        <v>-1587621.774852403</v>
       </c>
     </row>
     <row r="63">
@@ -2876,31 +2876,31 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="D63" t="n">
-        <v>276</v>
+        <v>353</v>
       </c>
       <c r="E63" t="n">
-        <v>393423.6681930316</v>
+        <v>737684.0221739078</v>
       </c>
       <c r="F63" t="n">
-        <v>-18512.80312540646</v>
+        <v>-20047.82474752256</v>
       </c>
       <c r="G63" t="n">
-        <v>54452.25976800311</v>
+        <v>113899.4138082542</v>
       </c>
       <c r="H63" t="n">
-        <v>5929.417557970974</v>
+        <v>8959.462020408107</v>
       </c>
       <c r="I63" t="n">
-        <v>-4112.14167730219</v>
+        <v>-1828.080031993179</v>
       </c>
       <c r="J63" t="n">
-        <v>7033.585945193399</v>
+        <v>7601.727297695542</v>
       </c>
       <c r="K63" t="n">
-        <v>-1946869.161399815</v>
+        <v>-849937.7526784956</v>
       </c>
     </row>
     <row r="64">
@@ -2915,31 +2915,31 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="D64" t="n">
-        <v>276</v>
+        <v>363</v>
       </c>
       <c r="E64" t="n">
-        <v>-697293.5715979688</v>
+        <v>-673215.4010497661</v>
       </c>
       <c r="F64" t="n">
-        <v>-46606.67913512616</v>
+        <v>-20658.57366376413</v>
       </c>
       <c r="G64" t="n">
-        <v>19028.26334016675</v>
+        <v>12192.60112765218</v>
       </c>
       <c r="H64" t="n">
-        <v>2609.518904326229</v>
+        <v>1451.178625676712</v>
       </c>
       <c r="I64" t="n">
-        <v>-12025.35394269675</v>
+        <v>-8138.503984015411</v>
       </c>
       <c r="J64" t="n">
-        <v>5980.921228096108</v>
+        <v>3436.936607827289</v>
       </c>
       <c r="K64" t="n">
-        <v>-2644162.732997784</v>
+        <v>-1523153.153728262</v>
       </c>
     </row>
     <row r="65">
@@ -2954,31 +2954,31 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>2008</v>
+        <v>2013</v>
       </c>
       <c r="D65" t="n">
-        <v>303</v>
+        <v>383</v>
       </c>
       <c r="E65" t="n">
-        <v>-763173.7560777623</v>
+        <v>-999722.8841589823</v>
       </c>
       <c r="F65" t="n">
-        <v>-70907.2072196057</v>
+        <v>-118970.0564558287</v>
       </c>
       <c r="G65" t="n">
-        <v>21342.95825366138</v>
+        <v>15500.59453928302</v>
       </c>
       <c r="H65" t="n">
-        <v>1161.260446669155</v>
+        <v>1505.983892989243</v>
       </c>
       <c r="I65" t="n">
-        <v>-10490.97599352949</v>
+        <v>-8272.106923455836</v>
       </c>
       <c r="J65" t="n">
-        <v>6339.458432970385</v>
+        <v>11455.15360447142</v>
       </c>
       <c r="K65" t="n">
-        <v>-3407336.489075546</v>
+        <v>-2522876.037887244</v>
       </c>
     </row>
     <row r="66">
@@ -2993,31 +2993,31 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2009</v>
+        <v>2014</v>
       </c>
       <c r="D66" t="n">
-        <v>317</v>
+        <v>448</v>
       </c>
       <c r="E66" t="n">
-        <v>-541275.7211597976</v>
+        <v>-1662523.04160366</v>
       </c>
       <c r="F66" t="n">
-        <v>-41684.20055600411</v>
+        <v>-72605.35193399165</v>
       </c>
       <c r="G66" t="n">
-        <v>59438.23853745858</v>
+        <v>8001.004120644523</v>
       </c>
       <c r="H66" t="n">
-        <v>6384.312051098422</v>
+        <v>823.9941129648944</v>
       </c>
       <c r="I66" t="n">
-        <v>-12918.18321262167</v>
+        <v>-15405.69387837885</v>
       </c>
       <c r="J66" t="n">
-        <v>8900.407554644309</v>
+        <v>7103.550462797704</v>
       </c>
       <c r="K66" t="n">
-        <v>-3948612.210235344</v>
+        <v>-4185399.079490904</v>
       </c>
     </row>
     <row r="67">
@@ -3032,31 +3032,31 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2010</v>
+        <v>2015</v>
       </c>
       <c r="D67" t="n">
-        <v>365</v>
+        <v>511</v>
       </c>
       <c r="E67" t="n">
-        <v>703602.2785569279</v>
+        <v>441348.5118473473</v>
       </c>
       <c r="F67" t="n">
-        <v>-54248.19948097832</v>
+        <v>-65973.57893859851</v>
       </c>
       <c r="G67" t="n">
-        <v>72835.42036691456</v>
+        <v>152215.7323642973</v>
       </c>
       <c r="H67" t="n">
-        <v>9215.49108779008</v>
+        <v>8465.070725359903</v>
       </c>
       <c r="I67" t="n">
-        <v>-2823.986900952769</v>
+        <v>-7690.329431248361</v>
       </c>
       <c r="J67" t="n">
-        <v>6917.97975604383</v>
+        <v>12758.74920093314</v>
       </c>
       <c r="K67" t="n">
-        <v>-3245009.931678416</v>
+        <v>-3744050.567643556</v>
       </c>
     </row>
     <row r="68">
@@ -3071,31 +3071,31 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
       <c r="D68" t="n">
-        <v>353</v>
+        <v>458</v>
       </c>
       <c r="E68" t="n">
-        <v>741846.6628882845</v>
+        <v>905681.5988677152</v>
       </c>
       <c r="F68" t="n">
-        <v>-20047.82474752256</v>
+        <v>-86727.25206400779</v>
       </c>
       <c r="G68" t="n">
-        <v>113899.4138082542</v>
+        <v>98517.87519416111</v>
       </c>
       <c r="H68" t="n">
-        <v>8959.462020408107</v>
+        <v>9929.932066962232</v>
       </c>
       <c r="I68" t="n">
-        <v>-1828.080031993179</v>
+        <v>-2662.693881051784</v>
       </c>
       <c r="J68" t="n">
-        <v>7628.535723240002</v>
+        <v>8623.125497233288</v>
       </c>
       <c r="K68" t="n">
-        <v>-2503163.268790131</v>
+        <v>-2838368.968775841</v>
       </c>
     </row>
     <row r="69">
@@ -3110,31 +3110,31 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
       <c r="D69" t="n">
-        <v>363</v>
+        <v>453</v>
       </c>
       <c r="E69" t="n">
-        <v>-675263.6884908832</v>
+        <v>1079524.45288021</v>
       </c>
       <c r="F69" t="n">
-        <v>-20658.57366376413</v>
+        <v>-49960.55808429873</v>
       </c>
       <c r="G69" t="n">
-        <v>12192.60112765218</v>
+        <v>114488.6818921621</v>
       </c>
       <c r="H69" t="n">
-        <v>1451.178625676712</v>
+        <v>9616.242831142656</v>
       </c>
       <c r="I69" t="n">
-        <v>-8179.477744509682</v>
+        <v>-1552.867690780908</v>
       </c>
       <c r="J69" t="n">
-        <v>3446.193125261715</v>
+        <v>8207.081177600388</v>
       </c>
       <c r="K69" t="n">
-        <v>-3178426.957281015</v>
+        <v>-1758844.515895631</v>
       </c>
     </row>
     <row r="70">
@@ -3149,31 +3149,31 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>2013</v>
+        <v>2018</v>
       </c>
       <c r="D70" t="n">
-        <v>383</v>
+        <v>432</v>
       </c>
       <c r="E70" t="n">
-        <v>-1003521.501221736</v>
+        <v>-464490.1900605655</v>
       </c>
       <c r="F70" t="n">
-        <v>-118970.0564558287</v>
+        <v>-63811.27361143316</v>
       </c>
       <c r="G70" t="n">
-        <v>15500.59453928302</v>
+        <v>52161.12970464121</v>
       </c>
       <c r="H70" t="n">
-        <v>1505.983892989243</v>
+        <v>1846.616903736069</v>
       </c>
       <c r="I70" t="n">
-        <v>-8272.106923455836</v>
+        <v>-5118.900635079496</v>
       </c>
       <c r="J70" t="n">
-        <v>11465.18638996857</v>
+        <v>5851.659229394421</v>
       </c>
       <c r="K70" t="n">
-        <v>-4181948.458502751</v>
+        <v>-2223334.705956196</v>
       </c>
     </row>
     <row r="71">
@@ -3188,31 +3188,31 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
       <c r="D71" t="n">
-        <v>448</v>
+        <v>430</v>
       </c>
       <c r="E71" t="n">
-        <v>-1665251.94770607</v>
+        <v>486111.3177017182</v>
       </c>
       <c r="F71" t="n">
-        <v>-72605.35193399165</v>
+        <v>-163510.3953686342</v>
       </c>
       <c r="G71" t="n">
-        <v>8705.328492463244</v>
+        <v>38640.53798155527</v>
       </c>
       <c r="H71" t="n">
-        <v>823.9941129648944</v>
+        <v>7168.511282302066</v>
       </c>
       <c r="I71" t="n">
-        <v>-15493.68539258295</v>
+        <v>-2279.725895239539</v>
       </c>
       <c r="J71" t="n">
-        <v>7119.628385731306</v>
+        <v>9379.656966494984</v>
       </c>
       <c r="K71" t="n">
-        <v>-5847200.406208821</v>
+        <v>-1737223.388254478</v>
       </c>
     </row>
     <row r="72">
@@ -3227,31 +3227,31 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="D72" t="n">
-        <v>511</v>
+        <v>402</v>
       </c>
       <c r="E72" t="n">
-        <v>441058.3350370392</v>
+        <v>-1445173.731020216</v>
       </c>
       <c r="F72" t="n">
-        <v>-65973.57893859851</v>
+        <v>-236843.4501267911</v>
       </c>
       <c r="G72" t="n">
-        <v>152215.7323642973</v>
+        <v>130379.5618599003</v>
       </c>
       <c r="H72" t="n">
-        <v>8659.8014614574</v>
+        <v>963.3508453592239</v>
       </c>
       <c r="I72" t="n">
-        <v>-7690.329431248361</v>
+        <v>-11749.67970199311</v>
       </c>
       <c r="J72" t="n">
-        <v>12761.64202311127</v>
+        <v>16034.92655795176</v>
       </c>
       <c r="K72" t="n">
-        <v>-5406142.071171781</v>
+        <v>-3182397.119274694</v>
       </c>
     </row>
     <row r="73">
@@ -3266,31 +3266,31 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
       <c r="D73" t="n">
-        <v>458</v>
+        <v>515</v>
       </c>
       <c r="E73" t="n">
-        <v>908966.0034602899</v>
+        <v>-1432762.360644108</v>
       </c>
       <c r="F73" t="n">
-        <v>-86727.25206400779</v>
+        <v>-51671.1325380028</v>
       </c>
       <c r="G73" t="n">
-        <v>98517.87519416111</v>
+        <v>98651.77801627608</v>
       </c>
       <c r="H73" t="n">
-        <v>9929.932066962232</v>
+        <v>3477.961794360886</v>
       </c>
       <c r="I73" t="n">
-        <v>-2693.016916099104</v>
+        <v>-16911.56649477475</v>
       </c>
       <c r="J73" t="n">
-        <v>8634.316722916103</v>
+        <v>9484.422766217413</v>
       </c>
       <c r="K73" t="n">
-        <v>-4497176.067711491</v>
+        <v>-4615159.479918802</v>
       </c>
     </row>
     <row r="74">
@@ -3305,31 +3305,31 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="D74" t="n">
-        <v>453</v>
+        <v>389</v>
       </c>
       <c r="E74" t="n">
-        <v>1078005.67199288</v>
+        <v>-540919.2954915673</v>
       </c>
       <c r="F74" t="n">
-        <v>-49960.55808429873</v>
+        <v>-32228.87936647474</v>
       </c>
       <c r="G74" t="n">
-        <v>114488.6818921621</v>
+        <v>51796.54640988007</v>
       </c>
       <c r="H74" t="n">
-        <v>9616.242831142656</v>
+        <v>3726.87796831587</v>
       </c>
       <c r="I74" t="n">
-        <v>-1552.867690780908</v>
+        <v>-10277.16985511434</v>
       </c>
       <c r="J74" t="n">
-        <v>8211.282718843589</v>
+        <v>5472.080114286887</v>
       </c>
       <c r="K74" t="n">
-        <v>-3419170.395718611</v>
+        <v>-5156078.775410369</v>
       </c>
     </row>
     <row r="75">
@@ -3344,31 +3344,31 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="D75" t="n">
-        <v>432</v>
+        <v>366</v>
       </c>
       <c r="E75" t="n">
-        <v>-459908.4000558979</v>
+        <v>2341473.103461097</v>
       </c>
       <c r="F75" t="n">
-        <v>-63811.27361143316</v>
+        <v>-9176.279848951432</v>
       </c>
       <c r="G75" t="n">
-        <v>52161.12970464121</v>
+        <v>250320.1844219764</v>
       </c>
       <c r="H75" t="n">
-        <v>1846.616903736069</v>
+        <v>20358.68365510694</v>
       </c>
       <c r="I75" t="n">
-        <v>-5186.595621498279</v>
+        <v>-819.7325868986527</v>
       </c>
       <c r="J75" t="n">
-        <v>5887.344173176242</v>
+        <v>16367.22832578889</v>
       </c>
       <c r="K75" t="n">
-        <v>-3879078.795774509</v>
+        <v>-2814605.671949273</v>
       </c>
     </row>
     <row r="76">
@@ -3383,31 +3383,31 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="D76" t="n">
-        <v>430</v>
+        <v>398</v>
       </c>
       <c r="E76" t="n">
-        <v>479540.4383893254</v>
+        <v>163996.2372147293</v>
       </c>
       <c r="F76" t="n">
-        <v>-163510.3953686342</v>
+        <v>-18590.75931946619</v>
       </c>
       <c r="G76" t="n">
-        <v>38640.53798155527</v>
+        <v>23707.31402813873</v>
       </c>
       <c r="H76" t="n">
-        <v>7168.511282302066</v>
+        <v>3578.493076943287</v>
       </c>
       <c r="I76" t="n">
-        <v>-2279.725895239539</v>
+        <v>-3118.911797757518</v>
       </c>
       <c r="J76" t="n">
-        <v>9426.682417316906</v>
+        <v>3154.764436916405</v>
       </c>
       <c r="K76" t="n">
-        <v>-3399538.357385184</v>
+        <v>-2650609.434734543</v>
       </c>
     </row>
     <row r="77">
@@ -3422,226 +3422,31 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="D77" t="n">
-        <v>402</v>
+        <v>330</v>
       </c>
       <c r="E77" t="n">
-        <v>-1449377.377708651</v>
+        <v>304557.8550354227</v>
       </c>
       <c r="F77" t="n">
-        <v>-238703.4008793693</v>
+        <v>-35839.63292258437</v>
       </c>
       <c r="G77" t="n">
-        <v>130379.5618599003</v>
+        <v>58077.08260658821</v>
       </c>
       <c r="H77" t="n">
-        <v>963.3508453592239</v>
+        <v>6139.486992120146</v>
       </c>
       <c r="I77" t="n">
-        <v>-11796.03725263298</v>
+        <v>-2955.027718837906</v>
       </c>
       <c r="J77" t="n">
-        <v>16104.43803042932</v>
+        <v>5703.397738549813</v>
       </c>
       <c r="K77" t="n">
-        <v>-4848915.735093835</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D78" t="n">
-        <v>515</v>
-      </c>
-      <c r="E78" t="n">
-        <v>-1437292.294685258</v>
-      </c>
-      <c r="F78" t="n">
-        <v>-51671.1325380028</v>
-      </c>
-      <c r="G78" t="n">
-        <v>98651.77801627608</v>
-      </c>
-      <c r="H78" t="n">
-        <v>3477.961794360886</v>
-      </c>
-      <c r="I78" t="n">
-        <v>-17446.03077321786</v>
-      </c>
-      <c r="J78" t="n">
-        <v>9497.057271328224</v>
-      </c>
-      <c r="K78" t="n">
-        <v>-6286208.029779092</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>2022</v>
-      </c>
-      <c r="D79" t="n">
-        <v>389</v>
-      </c>
-      <c r="E79" t="n">
-        <v>-548779.8180501496</v>
-      </c>
-      <c r="F79" t="n">
-        <v>-32228.87936647474</v>
-      </c>
-      <c r="G79" t="n">
-        <v>51796.54640988007</v>
-      </c>
-      <c r="H79" t="n">
-        <v>3726.87796831587</v>
-      </c>
-      <c r="I79" t="n">
-        <v>-10277.16985511434</v>
-      </c>
-      <c r="J79" t="n">
-        <v>5539.556422910265</v>
-      </c>
-      <c r="K79" t="n">
-        <v>-6834987.847829242</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D80" t="n">
-        <v>366</v>
-      </c>
-      <c r="E80" t="n">
-        <v>2391283.627972406</v>
-      </c>
-      <c r="F80" t="n">
-        <v>-9176.279848951432</v>
-      </c>
-      <c r="G80" t="n">
-        <v>274933.1593075962</v>
-      </c>
-      <c r="H80" t="n">
-        <v>20358.68365510694</v>
-      </c>
-      <c r="I80" t="n">
-        <v>-819.7325868986527</v>
-      </c>
-      <c r="J80" t="n">
-        <v>17590.30832353252</v>
-      </c>
-      <c r="K80" t="n">
-        <v>-4443704.219856836</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D81" t="n">
-        <v>398</v>
-      </c>
-      <c r="E81" t="n">
-        <v>157782.4540429347</v>
-      </c>
-      <c r="F81" t="n">
-        <v>-20554.25146014365</v>
-      </c>
-      <c r="G81" t="n">
-        <v>23707.31402813873</v>
-      </c>
-      <c r="H81" t="n">
-        <v>3578.493076943287</v>
-      </c>
-      <c r="I81" t="n">
-        <v>-3201.651271602526</v>
-      </c>
-      <c r="J81" t="n">
-        <v>3237.850190527096</v>
-      </c>
-      <c r="K81" t="n">
-        <v>-4285921.765813901</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Sacramento</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Primary</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>2025</v>
-      </c>
-      <c r="D82" t="n">
-        <v>330</v>
-      </c>
-      <c r="E82" t="n">
-        <v>326347.9190373168</v>
-      </c>
-      <c r="F82" t="n">
-        <v>-35839.63292258437</v>
-      </c>
-      <c r="G82" t="n">
-        <v>80274.50328299768</v>
-      </c>
-      <c r="H82" t="n">
-        <v>6139.486992120146</v>
-      </c>
-      <c r="I82" t="n">
-        <v>-2955.027718837906</v>
-      </c>
-      <c r="J82" t="n">
-        <v>6461.789610385143</v>
-      </c>
-      <c r="K82" t="n">
-        <v>-3959573.846776584</v>
+        <v>-2346051.57969912</v>
       </c>
     </row>
   </sheetData>
